--- a/graphs/practica_Ib/dades_Ib.xlsx
+++ b/graphs/practica_Ib/dades_Ib.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Miguel\UAB\TERCER\LAB Termo\Repositori\graphs\practica_Ib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BD10BF-D25B-4AE0-8EDA-14307223113F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907991D0-8849-4152-9DCF-75E0AC1E907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,25 +434,42 @@
       <c r="D1">
         <v>24.7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="E1">
+        <v>0</v>
+      </c>
+      <c r="F1">
+        <v>0</v>
+      </c>
+      <c r="G1">
+        <v>0.21</v>
+      </c>
+      <c r="H1">
+        <v>10.3</v>
+      </c>
+      <c r="I1">
+        <v>85.2</v>
+      </c>
+      <c r="J1">
+        <v>0.37</v>
+      </c>
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>10</v>
       </c>
-      <c r="V1" s="3"/>
       <c r="X1" s="3"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -468,31 +485,46 @@
       <c r="D2">
         <v>24.9</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1">
-        <f>((M2/$N$2) -1)/$O$2</f>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="H2">
+        <v>15.2</v>
+      </c>
+      <c r="I2" s="1">
+        <v>95.8</v>
+      </c>
+      <c r="J2">
+        <v>0.95</v>
+      </c>
+      <c r="L2" s="1">
+        <f t="shared" ref="L2:L43" si="0">((O2/$P$2) -1)/$Q$2</f>
         <v>50.388703988872905</v>
       </c>
-      <c r="K2">
-        <f>A2*B2*1000</f>
+      <c r="M2">
+        <f t="shared" ref="M2:M43" si="1">A2*B2*1000</f>
         <v>65600</v>
       </c>
-      <c r="L2">
-        <f>LOG(K2)</f>
+      <c r="N2">
+        <f>LOG(M2)</f>
         <v>4.8169038393756605</v>
       </c>
-      <c r="M2">
-        <f>A2/(B2/1000)</f>
+      <c r="O2">
+        <f t="shared" ref="O2:O43" si="2">A2/(B2/1000)</f>
         <v>60.975609756097569</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>49.1</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>4.7999999999999996E-3</v>
       </c>
-      <c r="V2" s="3"/>
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -508,23 +540,40 @@
       <c r="D3">
         <v>24.6</v>
       </c>
-      <c r="J3" s="1">
-        <f t="shared" ref="J3:J43" si="0">((M3/$N$2) -1)/$O$2</f>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>44.7</v>
+      </c>
+      <c r="G3">
+        <v>0.26</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="I3">
+        <v>101</v>
+      </c>
+      <c r="J3">
+        <v>1.17</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" si="0"/>
         <v>76.434546672316401</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K44" si="1">A3*B3*1000</f>
+      <c r="M3">
+        <f t="shared" si="1"/>
         <v>134100.00000000003</v>
       </c>
-      <c r="L3">
-        <f t="shared" ref="L3:L43" si="2">LOG(K3)</f>
+      <c r="N3">
+        <f t="shared" ref="N3:N43" si="3">LOG(M3)</f>
         <v>5.1274287778515992</v>
       </c>
-      <c r="M3">
-        <f t="shared" ref="M3:M43" si="3">A3/(B3/1000)</f>
+      <c r="O3">
+        <f t="shared" si="2"/>
         <v>67.114093959731534</v>
       </c>
-      <c r="V3" s="3"/>
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
@@ -540,24 +589,40 @@
       <c r="D4" s="1">
         <v>24.4</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="J4" s="1">
+      <c r="E4">
+        <v>5.2</v>
+      </c>
+      <c r="F4">
+        <v>62.2</v>
+      </c>
+      <c r="G4">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H4">
+        <v>21.3</v>
+      </c>
+      <c r="I4">
+        <v>106.5</v>
+      </c>
+      <c r="J4">
+        <v>1.52</v>
+      </c>
+      <c r="L4" s="1">
         <f t="shared" si="0"/>
         <v>146.39038600489411</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <f t="shared" si="1"/>
         <v>323440</v>
       </c>
-      <c r="L4">
-        <f t="shared" si="2"/>
+      <c r="N4">
+        <f t="shared" si="3"/>
         <v>5.5097937283256178</v>
       </c>
-      <c r="M4">
-        <f t="shared" si="3"/>
+      <c r="O4">
+        <f t="shared" si="2"/>
         <v>83.60128617363344</v>
       </c>
-      <c r="V4" s="3"/>
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
@@ -570,23 +635,40 @@
       <c r="C5" s="1">
         <v>0.35</v>
       </c>
-      <c r="J5" s="1">
+      <c r="E5">
+        <v>7.2</v>
+      </c>
+      <c r="F5">
+        <v>72.3</v>
+      </c>
+      <c r="G5">
+        <v>0.35</v>
+      </c>
+      <c r="H5">
+        <v>23.9</v>
+      </c>
+      <c r="I5">
+        <v>110.8</v>
+      </c>
+      <c r="J5">
+        <v>1.95</v>
+      </c>
+      <c r="L5" s="1">
         <f t="shared" si="0"/>
         <v>214.21020977878442</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <f t="shared" si="1"/>
         <v>520559.99999999994</v>
       </c>
-      <c r="L5">
-        <f t="shared" si="2"/>
+      <c r="N5">
+        <f t="shared" si="3"/>
         <v>5.716470793725799</v>
       </c>
-      <c r="M5">
-        <f t="shared" si="3"/>
+      <c r="O5">
+        <f t="shared" si="2"/>
         <v>99.585062240663902</v>
       </c>
-      <c r="V5" s="3"/>
       <c r="X5" s="3"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
@@ -599,23 +681,40 @@
       <c r="C6" s="1">
         <v>0.46</v>
       </c>
-      <c r="J6" s="1">
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>79</v>
+      </c>
+      <c r="G6">
+        <v>0.46</v>
+      </c>
+      <c r="H6">
+        <v>27.8</v>
+      </c>
+      <c r="I6">
+        <v>116.7</v>
+      </c>
+      <c r="J6">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="L6" s="1">
         <f t="shared" si="0"/>
         <v>275.05113133448486</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <f t="shared" si="1"/>
         <v>711000</v>
       </c>
-      <c r="L6">
-        <f t="shared" si="2"/>
+      <c r="N6">
+        <f t="shared" si="3"/>
         <v>5.8518696007297661</v>
       </c>
-      <c r="M6">
-        <f t="shared" si="3"/>
+      <c r="O6">
+        <f t="shared" si="2"/>
         <v>113.92405063291139</v>
       </c>
-      <c r="V6" s="3"/>
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -628,23 +727,40 @@
       <c r="C7" s="1">
         <v>0.37</v>
       </c>
-      <c r="J7" s="1">
+      <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>87.3</v>
+      </c>
+      <c r="G7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H7">
+        <v>32.1</v>
+      </c>
+      <c r="I7">
+        <v>123.3</v>
+      </c>
+      <c r="J7">
+        <v>3.29</v>
+      </c>
+      <c r="L7" s="1">
         <f t="shared" si="0"/>
         <v>304.61650873787653</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <f t="shared" si="1"/>
         <v>877560.00000000012</v>
       </c>
-      <c r="L7">
-        <f t="shared" si="2"/>
+      <c r="N7">
+        <f t="shared" si="3"/>
         <v>5.9432768194718726</v>
       </c>
-      <c r="M7">
-        <f t="shared" si="3"/>
+      <c r="O7">
+        <f t="shared" si="2"/>
         <v>120.89201877934273</v>
       </c>
-      <c r="V7" s="3"/>
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -657,23 +773,40 @@
       <c r="C8" s="1">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J8" s="1">
+      <c r="E8">
+        <v>15.1</v>
+      </c>
+      <c r="F8">
+        <v>93.9</v>
+      </c>
+      <c r="G8">
+        <v>0.7</v>
+      </c>
+      <c r="H8">
+        <v>35</v>
+      </c>
+      <c r="I8">
+        <v>127.6</v>
+      </c>
+      <c r="J8">
+        <v>3.92</v>
+      </c>
+      <c r="L8" s="1">
         <f t="shared" si="0"/>
         <v>374.90259959920024</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <f t="shared" si="1"/>
         <v>1047599.9999999999</v>
       </c>
-      <c r="L8">
-        <f t="shared" si="2"/>
+      <c r="N8">
+        <f t="shared" si="3"/>
         <v>6.0201954897531946</v>
       </c>
-      <c r="M8">
-        <f t="shared" si="3"/>
+      <c r="O8">
+        <f t="shared" si="2"/>
         <v>137.45704467353951</v>
       </c>
-      <c r="V8" s="3"/>
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -686,41 +819,58 @@
       <c r="C9" s="1">
         <v>0.7</v>
       </c>
-      <c r="J9" s="1">
+      <c r="E9">
+        <v>18</v>
+      </c>
+      <c r="F9">
+        <v>99.3</v>
+      </c>
+      <c r="G9">
+        <v>0.95</v>
+      </c>
+      <c r="H9">
+        <v>37.9</v>
+      </c>
+      <c r="I9">
+        <v>131.9</v>
+      </c>
+      <c r="J9">
+        <v>4.62</v>
+      </c>
+      <c r="L9" s="1">
         <f t="shared" si="0"/>
         <v>473.98749012216342</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <f t="shared" si="1"/>
         <v>1417890</v>
       </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
+      <c r="N9">
+        <f t="shared" si="3"/>
         <v>6.1516425395592806</v>
       </c>
-      <c r="M9">
-        <f t="shared" si="3"/>
+      <c r="O9">
+        <f t="shared" si="2"/>
         <v>160.80937167199147</v>
-      </c>
-      <c r="O9" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" t="s">
-        <v>3</v>
       </c>
       <c r="Q9" t="s">
         <v>3</v>
       </c>
       <c r="R9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T9" t="s">
         <v>4</v>
       </c>
-      <c r="V9" s="3"/>
+      <c r="U9" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" t="s">
+        <v>4</v>
+      </c>
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
@@ -733,91 +883,125 @@
       <c r="C10" s="1">
         <v>0.95</v>
       </c>
-      <c r="J10" s="1">
+      <c r="E10">
+        <v>21.1</v>
+      </c>
+      <c r="F10">
+        <v>104.6</v>
+      </c>
+      <c r="G10">
+        <v>1.36</v>
+      </c>
+      <c r="H10">
+        <v>42</v>
+      </c>
+      <c r="I10">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="J10">
+        <v>5.67</v>
+      </c>
+      <c r="L10" s="1">
         <f t="shared" si="0"/>
         <v>464.88409321864549</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <f t="shared" si="1"/>
         <v>1456159.9999999998</v>
       </c>
-      <c r="L10">
-        <f t="shared" si="2"/>
+      <c r="N10">
+        <f t="shared" si="3"/>
         <v>6.1632090970233167</v>
       </c>
-      <c r="M10">
-        <f t="shared" si="3"/>
+      <c r="O10">
+        <f t="shared" si="2"/>
         <v>158.66388308977037</v>
       </c>
-      <c r="O10" t="s">
+      <c r="Q10" t="s">
         <v>0</v>
       </c>
-      <c r="P10" t="s">
+      <c r="R10" t="s">
         <v>1</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="S10" t="s">
         <v>2</v>
       </c>
-      <c r="R10" t="s">
+      <c r="T10" t="s">
         <v>0</v>
       </c>
-      <c r="S10" t="s">
+      <c r="U10" t="s">
         <v>1</v>
       </c>
-      <c r="T10" t="s">
+      <c r="V10" t="s">
         <v>2</v>
       </c>
-      <c r="V10" s="3"/>
       <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
-        <f>AVERAGE(O11,R11)</f>
+        <f>AVERAGE(Q11,T11)</f>
         <v>18</v>
       </c>
       <c r="B11">
-        <f>AVERAGE(P11,S11)</f>
+        <f>AVERAGE(R11,U11)</f>
         <v>100.15</v>
       </c>
       <c r="C11">
-        <f>AVERAGE(Q11,T11)</f>
+        <f>AVERAGE(S11,V11)</f>
         <v>1.06</v>
       </c>
-      <c r="J11" s="1">
+      <c r="E11">
+        <v>24</v>
+      </c>
+      <c r="F11">
+        <v>109.4</v>
+      </c>
+      <c r="G11">
+        <v>1.76</v>
+      </c>
+      <c r="H11">
+        <v>46</v>
+      </c>
+      <c r="I11">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="J11">
+        <v>6.72</v>
+      </c>
+      <c r="L11" s="1">
         <f t="shared" si="0"/>
         <v>554.27021551854159</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <f t="shared" si="1"/>
         <v>1802700</v>
       </c>
-      <c r="L11">
-        <f t="shared" si="2"/>
+      <c r="N11">
+        <f t="shared" si="3"/>
         <v>6.2559234587329007</v>
       </c>
-      <c r="M11">
-        <f t="shared" si="3"/>
+      <c r="O11">
+        <f t="shared" si="2"/>
         <v>179.73040439340988</v>
       </c>
-      <c r="O11" s="1">
+      <c r="Q11" s="1">
         <v>18</v>
       </c>
-      <c r="P11" s="1">
+      <c r="R11" s="1">
         <v>99.3</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="S11" s="1">
         <v>0.95</v>
       </c>
-      <c r="R11" s="1">
+      <c r="T11" s="1">
         <v>18</v>
       </c>
-      <c r="S11" s="1">
+      <c r="U11" s="1">
         <v>101</v>
       </c>
-      <c r="T11" s="1">
+      <c r="V11" s="1">
         <v>1.17</v>
       </c>
-      <c r="V11" s="3"/>
       <c r="X11" s="3"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -830,20 +1014,29 @@
       <c r="C12" s="1">
         <v>1.36</v>
       </c>
-      <c r="J12" s="1">
+      <c r="H12">
+        <v>50</v>
+      </c>
+      <c r="I12">
+        <v>148.5</v>
+      </c>
+      <c r="J12">
+        <v>7.95</v>
+      </c>
+      <c r="L12" s="1">
         <f t="shared" si="0"/>
         <v>647.57654998383919</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <f t="shared" si="1"/>
         <v>2207060</v>
       </c>
-      <c r="L12">
-        <f t="shared" si="2"/>
+      <c r="N12">
+        <f t="shared" si="3"/>
         <v>6.3438141398289485</v>
       </c>
-      <c r="M12">
-        <f t="shared" si="3"/>
+      <c r="O12">
+        <f t="shared" si="2"/>
         <v>201.72084130019121</v>
       </c>
       <c r="V12" s="3"/>
@@ -859,20 +1052,29 @@
       <c r="C13" s="1">
         <v>1.52</v>
       </c>
-      <c r="J13" s="1">
+      <c r="H13">
+        <v>54.2</v>
+      </c>
+      <c r="I13">
+        <v>154.4</v>
+      </c>
+      <c r="J13">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="L13" s="1">
         <f t="shared" si="0"/>
         <v>640.27494908350309</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <f t="shared" si="1"/>
         <v>2268450.0000000005</v>
       </c>
-      <c r="L13">
-        <f t="shared" si="2"/>
+      <c r="N13">
+        <f t="shared" si="3"/>
         <v>6.355729211213494</v>
       </c>
-      <c r="M13">
-        <f t="shared" si="3"/>
+      <c r="O13">
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="V13" s="3"/>
@@ -888,20 +1090,29 @@
       <c r="C14" s="1">
         <v>1.95</v>
       </c>
-      <c r="J14" s="1">
+      <c r="H14">
+        <v>60.2</v>
+      </c>
+      <c r="I14">
+        <v>162</v>
+      </c>
+      <c r="J14">
+        <v>11.48</v>
+      </c>
+      <c r="L14" s="1">
         <f t="shared" si="0"/>
         <v>706.90754887616083</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <f t="shared" si="1"/>
         <v>2648120</v>
       </c>
-      <c r="L14">
-        <f t="shared" si="2"/>
+      <c r="N14">
+        <f t="shared" si="3"/>
         <v>6.4229376613405487</v>
       </c>
-      <c r="M14">
-        <f t="shared" si="3"/>
+      <c r="O14">
+        <f t="shared" si="2"/>
         <v>215.70397111913357</v>
       </c>
       <c r="V14" s="3"/>
@@ -917,20 +1128,29 @@
       <c r="C15" s="1">
         <v>1.76</v>
       </c>
-      <c r="J15" s="1">
+      <c r="H15">
+        <v>64</v>
+      </c>
+      <c r="I15">
+        <v>64</v>
+      </c>
+      <c r="J15">
+        <v>12.96</v>
+      </c>
+      <c r="L15" s="1">
         <f t="shared" si="0"/>
         <v>722.4984206887907</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <f t="shared" si="1"/>
         <v>2625600.0000000005</v>
       </c>
-      <c r="L15">
-        <f t="shared" si="2"/>
+      <c r="N15">
+        <f t="shared" si="3"/>
         <v>6.4192285637090185</v>
       </c>
-      <c r="M15">
-        <f t="shared" si="3"/>
+      <c r="O15">
+        <f t="shared" si="2"/>
         <v>219.37842778793416</v>
       </c>
       <c r="V15" s="3"/>
@@ -946,20 +1166,29 @@
       <c r="C16" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="J16" s="1">
+      <c r="H16">
+        <v>68</v>
+      </c>
+      <c r="I16">
+        <v>172</v>
+      </c>
+      <c r="J16">
+        <v>14.56</v>
+      </c>
+      <c r="L16" s="1">
         <f t="shared" si="0"/>
         <v>802.43402961388404</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <f t="shared" si="1"/>
         <v>3244260</v>
       </c>
-      <c r="L16">
-        <f t="shared" si="2"/>
+      <c r="N16">
+        <f t="shared" si="3"/>
         <v>6.5111156519634461</v>
       </c>
-      <c r="M16">
-        <f t="shared" si="3"/>
+      <c r="O16">
+        <f t="shared" si="2"/>
         <v>238.21765209940017</v>
       </c>
       <c r="V16" s="3"/>
@@ -975,20 +1204,29 @@
       <c r="C17" s="1">
         <v>3.29</v>
       </c>
-      <c r="J17" s="1">
+      <c r="H17">
+        <v>72.2</v>
+      </c>
+      <c r="I17">
+        <v>177.2</v>
+      </c>
+      <c r="J17">
+        <v>16.420000000000002</v>
+      </c>
+      <c r="L17" s="1">
         <f t="shared" si="0"/>
         <v>896.30275205111309</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <f t="shared" si="1"/>
         <v>3957930.0000000005</v>
       </c>
-      <c r="L17">
-        <f t="shared" si="2"/>
+      <c r="N17">
+        <f t="shared" si="3"/>
         <v>6.5974681090006042</v>
       </c>
-      <c r="M17">
-        <f t="shared" si="3"/>
+      <c r="O17">
+        <f t="shared" si="2"/>
         <v>260.34063260340633</v>
       </c>
       <c r="V17" s="3"/>
@@ -1004,20 +1242,29 @@
       <c r="C18" s="1">
         <v>3.92</v>
       </c>
-      <c r="J18" s="1">
+      <c r="H18">
+        <v>78.2</v>
+      </c>
+      <c r="I18">
+        <v>184.1</v>
+      </c>
+      <c r="J18">
+        <v>18.940000000000001</v>
+      </c>
+      <c r="L18" s="1">
         <f t="shared" si="0"/>
         <v>955.51031418192031</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <f t="shared" si="1"/>
         <v>4466000</v>
       </c>
-      <c r="L18">
-        <f t="shared" si="2"/>
+      <c r="N18">
+        <f t="shared" si="3"/>
         <v>6.6499187187354192</v>
       </c>
-      <c r="M18">
-        <f t="shared" si="3"/>
+      <c r="O18">
+        <f t="shared" si="2"/>
         <v>274.29467084639498</v>
       </c>
       <c r="V18" s="3"/>
@@ -1033,20 +1280,30 @@
       <c r="C19" s="1">
         <v>4.62</v>
       </c>
-      <c r="J19" s="1">
+      <c r="G19" s="2"/>
+      <c r="H19">
+        <v>84</v>
+      </c>
+      <c r="I19">
+        <v>190.9</v>
+      </c>
+      <c r="J19">
+        <v>21.71</v>
+      </c>
+      <c r="L19" s="1">
         <f t="shared" si="0"/>
         <v>1010.8574893959347</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <f t="shared" si="1"/>
         <v>4999010</v>
       </c>
-      <c r="L19">
-        <f t="shared" si="2"/>
+      <c r="N19">
+        <f t="shared" si="3"/>
         <v>6.6988840055144374</v>
       </c>
-      <c r="M19">
-        <f t="shared" si="3"/>
+      <c r="O19">
+        <f t="shared" si="2"/>
         <v>287.3388931008339</v>
       </c>
       <c r="V19" s="3"/>
@@ -1062,20 +1319,29 @@
       <c r="C20" s="1">
         <v>5.67</v>
       </c>
-      <c r="J20" s="1">
+      <c r="H20">
+        <v>90.1</v>
+      </c>
+      <c r="I20">
+        <v>197.9</v>
+      </c>
+      <c r="J20">
+        <v>24.74</v>
+      </c>
+      <c r="L20" s="1">
         <f t="shared" si="0"/>
         <v>1084.9013495950821</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <f t="shared" si="1"/>
         <v>5787600</v>
       </c>
-      <c r="L20">
-        <f t="shared" si="2"/>
+      <c r="N20">
+        <f t="shared" si="3"/>
         <v>6.7624985079695072</v>
       </c>
-      <c r="M20">
-        <f t="shared" si="3"/>
+      <c r="O20">
+        <f t="shared" si="2"/>
         <v>304.78955007256894</v>
       </c>
       <c r="V20" s="3"/>
@@ -1091,20 +1357,29 @@
       <c r="C21" s="1">
         <v>6.72</v>
       </c>
-      <c r="J21" s="1">
+      <c r="H21">
+        <v>100.3</v>
+      </c>
+      <c r="I21">
+        <v>209.1</v>
+      </c>
+      <c r="J21">
+        <v>30.14</v>
+      </c>
+      <c r="L21" s="1">
         <f t="shared" si="0"/>
         <v>1154.6548297663339</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <f t="shared" si="1"/>
         <v>6587200</v>
       </c>
-      <c r="L21">
-        <f t="shared" si="2"/>
+      <c r="N21">
+        <f t="shared" si="3"/>
         <v>6.8187008496534105</v>
       </c>
-      <c r="M21">
-        <f t="shared" si="3"/>
+      <c r="O21">
+        <f t="shared" si="2"/>
         <v>321.22905027932961</v>
       </c>
       <c r="V21" s="3"/>
@@ -1120,20 +1395,29 @@
       <c r="C22" s="1">
         <v>7.95</v>
       </c>
-      <c r="J22" s="1">
+      <c r="H22">
+        <v>110.4</v>
+      </c>
+      <c r="I22">
+        <v>219.5</v>
+      </c>
+      <c r="J22">
+        <v>35.67</v>
+      </c>
+      <c r="L22" s="1">
         <f t="shared" si="0"/>
         <v>1220.300138748883</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <f t="shared" si="1"/>
         <v>7425000</v>
       </c>
-      <c r="L22">
-        <f t="shared" si="2"/>
+      <c r="N22">
+        <f t="shared" si="3"/>
         <v>6.8706964579892498</v>
       </c>
-      <c r="M22">
-        <f t="shared" si="3"/>
+      <c r="O22">
+        <f t="shared" si="2"/>
         <v>336.70033670033672</v>
       </c>
       <c r="V22" s="3"/>
@@ -1149,20 +1433,29 @@
       <c r="C23" s="1">
         <v>9.3800000000000008</v>
       </c>
-      <c r="J23" s="1">
+      <c r="H23">
+        <v>120.6</v>
+      </c>
+      <c r="I23">
+        <v>231.1</v>
+      </c>
+      <c r="J23">
+        <v>41.27</v>
+      </c>
+      <c r="L23" s="1">
         <f t="shared" si="0"/>
         <v>1281.128095001917</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <f t="shared" si="1"/>
         <v>8368480.0000000009</v>
       </c>
-      <c r="L23">
-        <f t="shared" si="2"/>
+      <c r="N23">
+        <f t="shared" si="3"/>
         <v>6.9226465825381043</v>
       </c>
-      <c r="M23">
-        <f t="shared" si="3"/>
+      <c r="O23">
+        <f t="shared" si="2"/>
         <v>351.03626943005179</v>
       </c>
       <c r="V23" s="3"/>
@@ -1178,20 +1471,29 @@
       <c r="C24" s="1">
         <v>11.48</v>
       </c>
-      <c r="J24" s="1">
+      <c r="H24">
+        <v>130.4</v>
+      </c>
+      <c r="I24">
+        <v>240.8</v>
+      </c>
+      <c r="J24">
+        <v>47.39</v>
+      </c>
+      <c r="L24" s="1">
         <f t="shared" si="0"/>
         <v>1368.4018086880728</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <f t="shared" si="1"/>
         <v>9752400</v>
       </c>
-      <c r="L24">
-        <f t="shared" si="2"/>
+      <c r="N24">
+        <f t="shared" si="3"/>
         <v>6.9891115058004551</v>
       </c>
-      <c r="M24">
-        <f t="shared" si="3"/>
+      <c r="O24">
+        <f t="shared" si="2"/>
         <v>371.60493827160496</v>
       </c>
       <c r="V24" s="3"/>
@@ -1207,20 +1509,29 @@
       <c r="C25" s="1">
         <v>12.96</v>
       </c>
-      <c r="J25" s="1">
+      <c r="H25">
+        <v>140.30000000000001</v>
+      </c>
+      <c r="I25">
+        <v>250.3</v>
+      </c>
+      <c r="J25">
+        <v>53.62</v>
+      </c>
+      <c r="L25" s="1">
         <f t="shared" si="0"/>
         <v>1417.7424174055147</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <f t="shared" si="1"/>
         <v>10688000</v>
       </c>
-      <c r="L25">
-        <f t="shared" si="2"/>
+      <c r="N25">
+        <f t="shared" si="3"/>
         <v>7.0288964451314708</v>
       </c>
-      <c r="M25">
-        <f t="shared" si="3"/>
+      <c r="O25">
+        <f t="shared" si="2"/>
         <v>383.23353293413169</v>
       </c>
       <c r="V25" s="3"/>
@@ -1236,20 +1547,29 @@
       <c r="C26" s="1">
         <v>14.56</v>
       </c>
-      <c r="J26" s="1">
+      <c r="H26">
+        <v>150.6</v>
+      </c>
+      <c r="I26">
+        <v>260</v>
+      </c>
+      <c r="J26">
+        <v>60.12</v>
+      </c>
+      <c r="L26" s="1">
         <f t="shared" si="0"/>
         <v>1469.1481551650643</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <f t="shared" si="1"/>
         <v>11696000</v>
       </c>
-      <c r="L26">
-        <f t="shared" si="2"/>
+      <c r="N26">
+        <f t="shared" si="3"/>
         <v>7.0680373596137853</v>
       </c>
-      <c r="M26">
-        <f t="shared" si="3"/>
+      <c r="O26">
+        <f t="shared" si="2"/>
         <v>395.34883720930236</v>
       </c>
       <c r="V26" s="3"/>
@@ -1265,20 +1585,29 @@
       <c r="C27" s="1">
         <v>16.420000000000002</v>
       </c>
-      <c r="J27" s="1">
+      <c r="H27">
+        <v>161.19999999999999</v>
+      </c>
+      <c r="I27">
+        <v>269.2</v>
+      </c>
+      <c r="J27">
+        <v>67.260000000000005</v>
+      </c>
+      <c r="L27" s="1">
         <f t="shared" si="0"/>
         <v>1520.4905377303121</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <f t="shared" si="1"/>
         <v>12793840</v>
       </c>
-      <c r="L27">
-        <f t="shared" si="2"/>
+      <c r="N27">
+        <f t="shared" si="3"/>
         <v>7.107000915120671</v>
       </c>
-      <c r="M27">
-        <f t="shared" si="3"/>
+      <c r="O27">
+        <f t="shared" si="2"/>
         <v>407.44920993227993</v>
       </c>
       <c r="V27" s="3"/>
@@ -1294,20 +1623,29 @@
       <c r="C28" s="1">
         <v>18.940000000000001</v>
       </c>
-      <c r="J28" s="1">
+      <c r="H28">
+        <v>169.9</v>
+      </c>
+      <c r="I28">
+        <v>276.8</v>
+      </c>
+      <c r="J28">
+        <v>72.94</v>
+      </c>
+      <c r="L28" s="1">
         <f t="shared" si="0"/>
         <v>1593.9797488230113</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <f t="shared" si="1"/>
         <v>14396620</v>
       </c>
-      <c r="L28">
-        <f t="shared" si="2"/>
+      <c r="N28">
+        <f t="shared" si="3"/>
         <v>7.1582605415638625</v>
       </c>
-      <c r="M28">
-        <f t="shared" si="3"/>
+      <c r="O28">
+        <f t="shared" si="2"/>
         <v>424.76914720260731</v>
       </c>
       <c r="V28" s="3"/>
@@ -1323,20 +1661,29 @@
       <c r="C29" s="1">
         <v>21.71</v>
       </c>
-      <c r="J29" s="1">
+      <c r="H29">
+        <v>180</v>
+      </c>
+      <c r="I29">
+        <v>285.3</v>
+      </c>
+      <c r="J29">
+        <v>79.92</v>
+      </c>
+      <c r="L29" s="1">
         <f t="shared" si="0"/>
         <v>1658.6937940373912</v>
       </c>
-      <c r="K29">
+      <c r="M29">
         <f t="shared" si="1"/>
         <v>16035600</v>
       </c>
-      <c r="L29">
-        <f t="shared" si="2"/>
+      <c r="N29">
+        <f t="shared" si="3"/>
         <v>7.2050852144555488</v>
       </c>
-      <c r="M29">
-        <f t="shared" si="3"/>
+      <c r="O29">
+        <f t="shared" si="2"/>
         <v>440.02095337873232</v>
       </c>
       <c r="V29" s="3"/>
@@ -1352,20 +1699,29 @@
       <c r="C30" s="1">
         <v>24.74</v>
       </c>
-      <c r="J30" s="1">
+      <c r="H30">
+        <v>190.4</v>
+      </c>
+      <c r="I30">
+        <v>294</v>
+      </c>
+      <c r="J30">
+        <v>87.23</v>
+      </c>
+      <c r="L30" s="1">
         <f t="shared" si="0"/>
         <v>1723.4404475094398</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <f t="shared" si="1"/>
         <v>17830790</v>
       </c>
-      <c r="L30">
-        <f t="shared" si="2"/>
+      <c r="N30">
+        <f t="shared" si="3"/>
         <v>7.2511705851854593</v>
       </c>
-      <c r="M30">
-        <f t="shared" si="3"/>
+      <c r="O30">
+        <f t="shared" si="2"/>
         <v>455.28044466902475</v>
       </c>
       <c r="V30" s="3"/>
@@ -1381,20 +1737,29 @@
       <c r="C31" s="1">
         <v>30.14</v>
       </c>
-      <c r="J31" s="1">
+      <c r="H31">
+        <v>200.7</v>
+      </c>
+      <c r="I31">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="J31">
+        <v>94.06</v>
+      </c>
+      <c r="L31" s="1">
         <f t="shared" si="0"/>
         <v>1826.9466936013555</v>
       </c>
-      <c r="K31">
+      <c r="M31">
         <f t="shared" si="1"/>
         <v>20972730</v>
       </c>
-      <c r="L31">
-        <f t="shared" si="2"/>
+      <c r="N31">
+        <f t="shared" si="3"/>
         <v>7.3216549658380901</v>
       </c>
-      <c r="M31">
-        <f t="shared" si="3"/>
+      <c r="O31">
+        <f t="shared" si="2"/>
         <v>479.67479674796743</v>
       </c>
       <c r="V31" s="3"/>
@@ -1410,20 +1775,29 @@
       <c r="C32" s="1">
         <v>35.67</v>
       </c>
-      <c r="J32" s="1">
+      <c r="H32">
+        <v>210.7</v>
+      </c>
+      <c r="I32">
+        <v>310</v>
+      </c>
+      <c r="J32">
+        <v>101.77</v>
+      </c>
+      <c r="L32" s="1">
         <f t="shared" si="0"/>
         <v>1925.7521878242692</v>
       </c>
-      <c r="K32">
+      <c r="M32">
         <f t="shared" si="1"/>
         <v>24232800.000000004</v>
       </c>
-      <c r="L32">
-        <f t="shared" si="2"/>
+      <c r="N32">
+        <f t="shared" si="3"/>
         <v>7.3844035979713203</v>
       </c>
-      <c r="M32">
-        <f t="shared" si="3"/>
+      <c r="O32">
+        <f t="shared" si="2"/>
         <v>502.96127562642374</v>
       </c>
       <c r="V32" s="3"/>
@@ -1439,20 +1813,29 @@
       <c r="C33" s="1">
         <v>41.27</v>
       </c>
-      <c r="J33" s="1">
+      <c r="H33">
+        <v>219.7</v>
+      </c>
+      <c r="I33">
+        <v>317</v>
+      </c>
+      <c r="J33">
+        <v>108</v>
+      </c>
+      <c r="L33" s="1">
         <f t="shared" si="0"/>
         <v>2005.9063650541714</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <f t="shared" si="1"/>
         <v>27870659.999999996</v>
       </c>
-      <c r="L33">
-        <f t="shared" si="2"/>
+      <c r="N33">
+        <f t="shared" si="3"/>
         <v>7.4451472532832419</v>
       </c>
-      <c r="M33">
-        <f t="shared" si="3"/>
+      <c r="O33">
+        <f t="shared" si="2"/>
         <v>521.85201211596711</v>
       </c>
       <c r="V33" s="3"/>
@@ -1468,20 +1851,20 @@
       <c r="C34" s="1">
         <v>47.39</v>
       </c>
-      <c r="J34" s="1">
+      <c r="L34" s="1">
         <f t="shared" si="0"/>
         <v>2089.3934114165727</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <f t="shared" si="1"/>
         <v>31400320.000000004</v>
       </c>
-      <c r="L34">
-        <f t="shared" si="2"/>
+      <c r="N34">
+        <f t="shared" si="3"/>
         <v>7.4969340739816888</v>
       </c>
-      <c r="M34">
-        <f t="shared" si="3"/>
+      <c r="O34">
+        <f t="shared" si="2"/>
         <v>541.5282392026578</v>
       </c>
       <c r="V34" s="3"/>
@@ -1497,20 +1880,20 @@
       <c r="C35" s="1">
         <v>53.62</v>
       </c>
-      <c r="J35" s="1">
+      <c r="L35" s="1">
         <f t="shared" si="0"/>
         <v>2170.0074981305534</v>
       </c>
-      <c r="K35">
+      <c r="M35">
         <f t="shared" si="1"/>
         <v>35117090.000000007</v>
       </c>
-      <c r="L35">
-        <f t="shared" si="2"/>
+      <c r="N35">
+        <f t="shared" si="3"/>
         <v>7.5455185206365831</v>
       </c>
-      <c r="M35">
-        <f t="shared" si="3"/>
+      <c r="O35">
+        <f t="shared" si="2"/>
         <v>560.52736715940875</v>
       </c>
       <c r="V35" s="3"/>
@@ -1526,20 +1909,20 @@
       <c r="C36" s="1">
         <v>60.12</v>
       </c>
-      <c r="J36" s="1">
+      <c r="L36" s="1">
         <f t="shared" si="0"/>
         <v>2249.3668076661966</v>
       </c>
-      <c r="K36">
+      <c r="M36">
         <f t="shared" si="1"/>
         <v>39156000</v>
       </c>
-      <c r="L36">
-        <f t="shared" si="2"/>
+      <c r="N36">
+        <f t="shared" si="3"/>
         <v>7.5927983198354996</v>
       </c>
-      <c r="M36">
-        <f t="shared" si="3"/>
+      <c r="O36">
+        <f t="shared" si="2"/>
         <v>579.23076923076917</v>
       </c>
       <c r="V36" s="3"/>
@@ -1555,20 +1938,20 @@
       <c r="C37" s="1">
         <v>67.260000000000005</v>
       </c>
-      <c r="J37" s="1">
+      <c r="L37" s="1">
         <f t="shared" si="0"/>
         <v>2332.4477796977594</v>
       </c>
-      <c r="K37">
+      <c r="M37">
         <f t="shared" si="1"/>
         <v>43395039.999999993</v>
       </c>
-      <c r="L37">
-        <f t="shared" si="2"/>
+      <c r="N37">
+        <f t="shared" si="3"/>
         <v>7.6374400930210111</v>
       </c>
-      <c r="M37">
-        <f t="shared" si="3"/>
+      <c r="O37">
+        <f t="shared" si="2"/>
         <v>598.81129271916791</v>
       </c>
       <c r="V37" s="3"/>
@@ -1584,20 +1967,20 @@
       <c r="C38" s="1">
         <v>72.94</v>
       </c>
-      <c r="J38" s="1">
+      <c r="L38" s="1">
         <f t="shared" si="0"/>
         <v>2396.0479380290312</v>
       </c>
-      <c r="K38">
+      <c r="M38">
         <f t="shared" si="1"/>
         <v>47028320.000000007</v>
       </c>
-      <c r="L38">
-        <f t="shared" si="2"/>
+      <c r="N38">
+        <f t="shared" si="3"/>
         <v>7.6723594646537663</v>
       </c>
-      <c r="M38">
-        <f t="shared" si="3"/>
+      <c r="O38">
+        <f t="shared" si="2"/>
         <v>613.80057803468208</v>
       </c>
       <c r="V38" s="3"/>
@@ -1613,20 +1996,20 @@
       <c r="C39" s="1">
         <v>79.92</v>
       </c>
-      <c r="J39" s="1">
+      <c r="L39" s="1">
         <f t="shared" si="0"/>
         <v>2468.6644029973809</v>
       </c>
-      <c r="K39">
+      <c r="M39">
         <f t="shared" si="1"/>
         <v>51354000</v>
       </c>
-      <c r="L39">
-        <f t="shared" si="2"/>
+      <c r="N39">
+        <f t="shared" si="3"/>
         <v>7.7105742767603829</v>
       </c>
-      <c r="M39">
-        <f t="shared" si="3"/>
+      <c r="O39">
+        <f t="shared" si="2"/>
         <v>630.91482649842271</v>
       </c>
       <c r="V39" s="3"/>
@@ -1642,20 +2025,20 @@
       <c r="C40" s="1">
         <v>87.23</v>
       </c>
-      <c r="J40" s="1">
+      <c r="L40" s="1">
         <f t="shared" si="0"/>
         <v>2539.5411049688041</v>
       </c>
-      <c r="K40">
+      <c r="M40">
         <f t="shared" si="1"/>
         <v>55977600</v>
       </c>
-      <c r="L40">
-        <f t="shared" si="2"/>
+      <c r="N40">
+        <f t="shared" si="3"/>
         <v>7.7480142744606129</v>
       </c>
-      <c r="M40">
-        <f t="shared" si="3"/>
+      <c r="O40">
+        <f t="shared" si="2"/>
         <v>647.61904761904771</v>
       </c>
       <c r="V40" s="3"/>
@@ -1671,20 +2054,20 @@
       <c r="C41" s="1">
         <v>94.06</v>
       </c>
-      <c r="J41" s="1">
+      <c r="L41" s="1">
         <f t="shared" si="0"/>
         <v>2607.732841948728</v>
       </c>
-      <c r="K41">
+      <c r="M41">
         <f t="shared" si="1"/>
         <v>60691679.999999993</v>
       </c>
-      <c r="L41">
-        <f t="shared" si="2"/>
+      <c r="N41">
+        <f t="shared" si="3"/>
         <v>7.7831291593166547</v>
       </c>
-      <c r="M41">
-        <f t="shared" si="3"/>
+      <c r="O41">
+        <f t="shared" si="2"/>
         <v>663.69047619047615</v>
       </c>
       <c r="V41" s="3"/>
@@ -1700,20 +2083,20 @@
       <c r="C42" s="1">
         <v>101.77</v>
       </c>
-      <c r="J42" s="1">
+      <c r="L42" s="1">
         <f t="shared" si="0"/>
         <v>2675.5661038477542</v>
       </c>
-      <c r="K42">
+      <c r="M42">
         <f t="shared" si="1"/>
         <v>65317000</v>
       </c>
-      <c r="L42">
-        <f t="shared" si="2"/>
+      <c r="N42">
+        <f t="shared" si="3"/>
         <v>7.8150262294423731</v>
       </c>
-      <c r="M42">
-        <f t="shared" si="3"/>
+      <c r="O42">
+        <f t="shared" si="2"/>
         <v>679.67741935483866</v>
       </c>
       <c r="V42" s="3"/>
@@ -1729,20 +2112,20 @@
       <c r="C43" s="1">
         <v>108</v>
       </c>
-      <c r="J43" s="1">
+      <c r="L43" s="1">
         <f t="shared" si="0"/>
         <v>2732.3486800259561</v>
       </c>
-      <c r="K43">
+      <c r="M43">
         <f t="shared" si="1"/>
         <v>69644900</v>
       </c>
-      <c r="L43">
-        <f t="shared" si="2"/>
+      <c r="N43">
+        <f t="shared" si="3"/>
         <v>7.842889319138262</v>
       </c>
-      <c r="M43">
-        <f t="shared" si="3"/>
+      <c r="O43">
+        <f t="shared" si="2"/>
         <v>693.05993690851733</v>
       </c>
       <c r="V43" s="3"/>
@@ -2078,6 +2461,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
